--- a/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A111293B-7C52-483B-ABDE-C39E52DC2A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8992928D-1B86-4449-9BA2-1B97C2596F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C7F57664-5CD8-4535-9981-920CB3E35E65}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C08350A9-F4F7-4F25-9270-7C3E492451D8}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42339636-9F97-4320-AEA9-8A857B2203F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0579C50-3CD6-4CD8-A89D-70CD55E5F895}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8992928D-1B86-4449-9BA2-1B97C2596F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D104A41-294E-41EA-BACB-C98DF215F46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C08350A9-F4F7-4F25-9270-7C3E492451D8}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{62B60421-B12B-4835-86FC-6F5858D4CE61}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0579C50-3CD6-4CD8-A89D-70CD55E5F895}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A40130-9A2D-466B-9B3E-FB2A7BC59B07}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-17_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D104A41-294E-41EA-BACB-C98DF215F46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9436422E-1EC2-4749-AD18-B3BD7C555536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{62B60421-B12B-4835-86FC-6F5858D4CE61}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{7DFBFC06-613A-4BC1-81A4-CCA521A84BB3}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A40130-9A2D-466B-9B3E-FB2A7BC59B07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32D3EA9-3042-4B6B-9CCE-5E9607BCA811}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
